--- a/InputData/trans/ICtPSFfL/Incremental Cost to Produce Substitute Fuel for LCFS.xlsx
+++ b/InputData/trans/ICtPSFfL/Incremental Cost to Produce Substitute Fuel for LCFS.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\ICtPSFfL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anima\OneDrive\Desktop\Models\eps-brazil-cpl2\InputData\trans\ICtPSFfL\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F439FF-3D63-43CC-8709-6DA3650446A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13800"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -28,10 +29,21 @@
     <definedName name="nonlignite_multiplier">#REF!</definedName>
     <definedName name="use_lifecycle_biofuel_EIs">[1]About!$A$61</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -172,7 +184,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -190,7 +202,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,6 +212,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -219,12 +237,12 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -243,7 +261,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
@@ -574,113 +592,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B5" s="4">
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" s="2">
         <v>947817.12</v>
       </c>
       <c r="B24" t="s">
@@ -694,20 +712,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:BE35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.3984375" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="30" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.45">
       <c r="B2">
         <v>2015</v>
       </c>
@@ -816,8 +839,68 @@
       <c r="AK2">
         <v>2050</v>
       </c>
+      <c r="AL2">
+        <v>2051</v>
+      </c>
+      <c r="AM2">
+        <v>2052</v>
+      </c>
+      <c r="AN2">
+        <v>2053</v>
+      </c>
+      <c r="AO2">
+        <v>2054</v>
+      </c>
+      <c r="AP2">
+        <v>2055</v>
+      </c>
+      <c r="AQ2">
+        <v>2056</v>
+      </c>
+      <c r="AR2">
+        <v>2057</v>
+      </c>
+      <c r="AS2">
+        <v>2058</v>
+      </c>
+      <c r="AT2">
+        <v>2059</v>
+      </c>
+      <c r="AU2">
+        <v>2060</v>
+      </c>
+      <c r="AV2">
+        <v>2061</v>
+      </c>
+      <c r="AW2">
+        <v>2062</v>
+      </c>
+      <c r="AX2">
+        <v>2063</v>
+      </c>
+      <c r="AY2">
+        <v>2064</v>
+      </c>
+      <c r="AZ2">
+        <v>2065</v>
+      </c>
+      <c r="BA2">
+        <v>2066</v>
+      </c>
+      <c r="BB2">
+        <v>2067</v>
+      </c>
+      <c r="BC2">
+        <v>2068</v>
+      </c>
+      <c r="BD2">
+        <v>2069</v>
+      </c>
+      <c r="BE2">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -929,8 +1012,88 @@
       <c r="AK3">
         <v>38.8994534841326</v>
       </c>
+      <c r="AL3" s="5">
+        <f>_xlfn.FORECAST.ETS(AL$2,$B3:$AK3,$B$2:$AK$2)</f>
+        <v>38.94450070499132</v>
+      </c>
+      <c r="AM3" s="5">
+        <f>_xlfn.FORECAST.ETS(AM$2,$B3:$AK3,$B$2:$AK$2)</f>
+        <v>38.989547925850033</v>
+      </c>
+      <c r="AN3" s="5">
+        <f t="shared" ref="AN3:BE8" si="0">_xlfn.FORECAST.ETS(AN$2,$B3:$AK3,$B$2:$AK$2)</f>
+        <v>39.034595146708753</v>
+      </c>
+      <c r="AO3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.079642367567473</v>
+      </c>
+      <c r="AP3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.124689588426186</v>
+      </c>
+      <c r="AQ3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.169736809284906</v>
+      </c>
+      <c r="AR3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.214784030143626</v>
+      </c>
+      <c r="AS3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.259831251002339</v>
+      </c>
+      <c r="AT3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.304878471861059</v>
+      </c>
+      <c r="AU3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.349925692719779</v>
+      </c>
+      <c r="AV3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.394972913578492</v>
+      </c>
+      <c r="AW3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.440020134437212</v>
+      </c>
+      <c r="AX3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.485067355295932</v>
+      </c>
+      <c r="AY3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.530114576154645</v>
+      </c>
+      <c r="AZ3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.575161797013365</v>
+      </c>
+      <c r="BA3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.620209017872085</v>
+      </c>
+      <c r="BB3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.665256238730805</v>
+      </c>
+      <c r="BC3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.710303459589518</v>
+      </c>
+      <c r="BD3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.755350680448238</v>
+      </c>
+      <c r="BE3" s="5">
+        <f t="shared" si="0"/>
+        <v>39.800397901306958</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1042,8 +1205,88 @@
       <c r="AK4">
         <v>47.526138928681398</v>
       </c>
+      <c r="AL4" s="5">
+        <f>AK4+AK4*($AK4-$AJ4)/$AJ4</f>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AM4" s="5">
+        <f>AL4+AL4*($AK4-$AJ4)/$AJ4</f>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AN4" s="5">
+        <f t="shared" ref="AN4:BE4" si="1">AM4+AM4*($AK4-$AJ4)/$AJ4</f>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AO4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AP4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AQ4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AR4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AS4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AT4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AU4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AV4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AW4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AX4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AY4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="AZ4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="BA4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="BB4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="BC4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="BD4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
+      <c r="BE4" s="5">
+        <f t="shared" si="1"/>
+        <v>47.526138928681398</v>
+      </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1155,8 +1398,88 @@
       <c r="AK5">
         <v>36.031200708728697</v>
       </c>
+      <c r="AL5">
+        <f t="shared" ref="AL4:BA11" si="2">_xlfn.FORECAST.ETS(AL$2,$B5:$AK5,$B$2:$AK$2)</f>
+        <v>36.765146386039419</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="2"/>
+        <v>37.530381198860184</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>38.295616011680956</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>39.060850824501728</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>39.826085637322493</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>40.591320450143265</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>41.356555262964037</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>42.121790075784801</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>42.887024888605573</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>43.652259701426345</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>44.41749451424711</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>45.182729327067882</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>45.947964139888654</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>46.713198952709419</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>47.478433765530191</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="0"/>
+        <v>48.243668578350963</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="0"/>
+        <v>49.008903391171735</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="0"/>
+        <v>49.774138203992507</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="0"/>
+        <v>50.539373016813272</v>
+      </c>
+      <c r="BE5">
+        <f t="shared" si="0"/>
+        <v>51.304607829634044</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1269,7 +1592,7 @@
         <v>41.934834775512002</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1282,7 +1605,7 @@
       <c r="D7">
         <v>18.885450227945402</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>19.0133949371196</v>
       </c>
       <c r="F7">
@@ -1381,8 +1704,88 @@
       <c r="AK7">
         <v>36.031508112322399</v>
       </c>
+      <c r="AL7">
+        <f t="shared" si="2"/>
+        <v>36.798122175395882</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="2"/>
+        <v>37.564798124077541</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>38.3314740727592</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>39.098150021440858</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>39.864825970122517</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>40.631501918804176</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>41.398177867485835</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>42.164853816167494</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>42.931529764849152</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>43.698205713530811</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>44.46488166221247</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>45.231557610894129</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>45.998233559575795</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>46.764909508257446</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>47.531585456939112</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="0"/>
+        <v>48.298261405620764</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="0"/>
+        <v>49.06493735430243</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="0"/>
+        <v>49.831613302984081</v>
+      </c>
+      <c r="BD7">
+        <f t="shared" si="0"/>
+        <v>50.598289251665747</v>
+      </c>
+      <c r="BE7">
+        <f t="shared" si="0"/>
+        <v>51.364965200347399</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1494,13 +1897,93 @@
       <c r="AK8">
         <v>39.309585492238803</v>
       </c>
+      <c r="AL8">
+        <f t="shared" si="2"/>
+        <v>39.818552387919347</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="2"/>
+        <v>40.342445652635703</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>40.86633891735206</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>41.390232182068416</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>41.91412544678478</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>42.438018711501137</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>42.961911976217493</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>43.48580524093385</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>44.009698505650206</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>44.533591770366563</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>45.057485035082919</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>45.581378299799276</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>46.105271564515633</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>46.629164829231989</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
+        <v>47.153058093948346</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="0"/>
+        <v>47.676951358664709</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="0"/>
+        <v>48.200844623381059</v>
+      </c>
+      <c r="BC8">
+        <f t="shared" si="0"/>
+        <v>48.724737888097422</v>
+      </c>
+      <c r="BD8">
+        <f t="shared" si="0"/>
+        <v>49.248631152813779</v>
+      </c>
+      <c r="BE8">
+        <f t="shared" si="0"/>
+        <v>49.772524417530136</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1612,8 +2095,88 @@
       <c r="AK10">
         <v>38.8994534841326</v>
       </c>
+      <c r="AL10" s="5">
+        <f t="shared" si="2"/>
+        <v>38.968954607353169</v>
+      </c>
+      <c r="AM10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.038455730573745</v>
+      </c>
+      <c r="AN10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.107956853794313</v>
+      </c>
+      <c r="AO10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.177457977014889</v>
+      </c>
+      <c r="AP10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.246959100235458</v>
+      </c>
+      <c r="AQ10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.316460223456026</v>
+      </c>
+      <c r="AR10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.385961346676602</v>
+      </c>
+      <c r="AS10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.455462469897171</v>
+      </c>
+      <c r="AT10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.524963593117747</v>
+      </c>
+      <c r="AU10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.594464716338315</v>
+      </c>
+      <c r="AV10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.663965839558891</v>
+      </c>
+      <c r="AW10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.73346696277946</v>
+      </c>
+      <c r="AX10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.802968086000028</v>
+      </c>
+      <c r="AY10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.872469209220604</v>
+      </c>
+      <c r="AZ10" s="5">
+        <f t="shared" si="2"/>
+        <v>39.941970332441173</v>
+      </c>
+      <c r="BA10" s="5">
+        <f t="shared" si="2"/>
+        <v>40.011471455661749</v>
+      </c>
+      <c r="BB10" s="5">
+        <f t="shared" ref="AM10:BE11" si="3">_xlfn.FORECAST.ETS(BB$2,$B10:$AK10,$B$2:$AK$2)</f>
+        <v>40.080972578882317</v>
+      </c>
+      <c r="BC10" s="5">
+        <f t="shared" si="3"/>
+        <v>40.150473702102886</v>
+      </c>
+      <c r="BD10" s="5">
+        <f t="shared" si="3"/>
+        <v>40.219974825323462</v>
+      </c>
+      <c r="BE10" s="5">
+        <f t="shared" si="3"/>
+        <v>40.28947594854403</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1725,1359 +2288,2159 @@
       <c r="AK11">
         <v>47.526138928681398</v>
       </c>
+      <c r="AL11" s="5">
+        <f t="shared" si="2"/>
+        <v>48.378390578474523</v>
+      </c>
+      <c r="AM11" s="5">
+        <f t="shared" si="3"/>
+        <v>48.805170155547465</v>
+      </c>
+      <c r="AN11" s="5">
+        <f t="shared" si="3"/>
+        <v>49.231949732620414</v>
+      </c>
+      <c r="AO11" s="5">
+        <f t="shared" si="3"/>
+        <v>49.658729309693356</v>
+      </c>
+      <c r="AP11" s="5">
+        <f t="shared" si="3"/>
+        <v>50.085508886766299</v>
+      </c>
+      <c r="AQ11" s="5">
+        <f t="shared" si="3"/>
+        <v>50.512288463839241</v>
+      </c>
+      <c r="AR11" s="5">
+        <f t="shared" si="3"/>
+        <v>50.939068040912183</v>
+      </c>
+      <c r="AS11" s="5">
+        <f t="shared" si="3"/>
+        <v>51.365847617985132</v>
+      </c>
+      <c r="AT11" s="5">
+        <f t="shared" si="3"/>
+        <v>51.792627195058074</v>
+      </c>
+      <c r="AU11" s="5">
+        <f t="shared" si="3"/>
+        <v>52.219406772131016</v>
+      </c>
+      <c r="AV11" s="5">
+        <f t="shared" si="3"/>
+        <v>52.646186349203958</v>
+      </c>
+      <c r="AW11" s="5">
+        <f t="shared" si="3"/>
+        <v>53.072965926276908</v>
+      </c>
+      <c r="AX11" s="5">
+        <f t="shared" si="3"/>
+        <v>53.49974550334985</v>
+      </c>
+      <c r="AY11" s="5">
+        <f t="shared" si="3"/>
+        <v>53.926525080422792</v>
+      </c>
+      <c r="AZ11" s="5">
+        <f t="shared" si="3"/>
+        <v>54.353304657495734</v>
+      </c>
+      <c r="BA11" s="5">
+        <f t="shared" si="3"/>
+        <v>54.780084234568676</v>
+      </c>
+      <c r="BB11" s="5">
+        <f t="shared" si="3"/>
+        <v>55.206863811641625</v>
+      </c>
+      <c r="BC11" s="5">
+        <f t="shared" si="3"/>
+        <v>55.633643388714567</v>
+      </c>
+      <c r="BD11" s="5">
+        <f t="shared" si="3"/>
+        <v>56.060422965787509</v>
+      </c>
+      <c r="BE11" s="5">
+        <f t="shared" si="3"/>
+        <v>56.487202542860452</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>0</v>
       </c>
       <c r="B14">
-        <f t="shared" ref="B14:AK14" si="0">B3/btu_per_EJ</f>
+        <f t="shared" ref="B14:AK14" si="4">B3/btu_per_EJ</f>
         <v>3.2534468284018547E-5</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.5737832403189339E-5</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8702280150073783E-5</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8932947027500934E-5</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8817163279941811E-5</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8994337651509501E-5</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.9185374681930201E-5</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.9249493189401668E-5</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8750424901854275E-5</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8697157933611182E-5</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8643108512727222E-5</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.858598946994448E-5</v>
       </c>
       <c r="N14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8524597031969414E-5</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8455602036743121E-5</v>
       </c>
       <c r="P14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8379726843017881E-5</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8288096649689652E-5</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.165972632377985E-5</v>
       </c>
       <c r="S14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.1527352624345722E-5</v>
       </c>
       <c r="T14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.1387140294163922E-5</v>
       </c>
       <c r="U14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.1216192960242484E-5</v>
       </c>
       <c r="V14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.4522641410497731E-5</v>
       </c>
       <c r="W14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.409600747587288E-5</v>
       </c>
       <c r="X14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.3872860563119181E-5</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.3218705168607418E-5</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.2355959582857818E-5</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.0298165334418315E-5</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.7909296844186139E-5</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.4612165929120589E-5</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.5361384822674651E-5</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.6125535573426656E-5</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.6904915774644164E-5</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.7699828952329217E-5</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.8510584666979533E-5</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.9337498666232791E-5</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.0180892986627953E-5</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>4.1041096075720387E-5</v>
       </c>
+      <c r="AL14">
+        <f t="shared" ref="AL14:BE14" si="5">AL3/btu_per_EJ</f>
+        <v>4.1088623409747358E-5</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="5"/>
+        <v>4.1136150743774323E-5</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="5"/>
+        <v>4.1183678077801287E-5</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="5"/>
+        <v>4.1231205411828259E-5</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="5"/>
+        <v>4.1278732745855217E-5</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="5"/>
+        <v>4.1326260079882188E-5</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="5"/>
+        <v>4.137378741390916E-5</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="5"/>
+        <v>4.1421314747936117E-5</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="5"/>
+        <v>4.1468842081963089E-5</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="5"/>
+        <v>4.151636941599006E-5</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="5"/>
+        <v>4.1563896750017018E-5</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="5"/>
+        <v>4.161142408404399E-5</v>
+      </c>
+      <c r="AX14">
+        <f t="shared" si="5"/>
+        <v>4.1658951418070961E-5</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="5"/>
+        <v>4.1706478752097919E-5</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="5"/>
+        <v>4.1754006086124891E-5</v>
+      </c>
+      <c r="BA14">
+        <f t="shared" si="5"/>
+        <v>4.1801533420151862E-5</v>
+      </c>
+      <c r="BB14">
+        <f t="shared" si="5"/>
+        <v>4.1849060754178827E-5</v>
+      </c>
+      <c r="BC14">
+        <f t="shared" si="5"/>
+        <v>4.1896588088205791E-5</v>
+      </c>
+      <c r="BD14">
+        <f t="shared" si="5"/>
+        <v>4.1944115422232763E-5</v>
+      </c>
+      <c r="BE14">
+        <f t="shared" si="5"/>
+        <v>4.1991642756259728E-5</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>1</v>
       </c>
       <c r="B15">
-        <f t="shared" ref="B15:AK15" si="1">B4/btu_per_EJ</f>
+        <f t="shared" ref="B15:AK15" si="6">B4/btu_per_EJ</f>
         <v>3.2684379576442442E-5</v>
       </c>
       <c r="C15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.5904835850454043E-5</v>
       </c>
       <c r="D15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8910055053500406E-5</v>
       </c>
       <c r="E15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.9116998612867117E-5</v>
       </c>
       <c r="F15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.9307937326779875E-5</v>
       </c>
       <c r="G15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.9480481057637784E-5</v>
       </c>
       <c r="H15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.9613935449504121E-5</v>
       </c>
       <c r="I15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.9727482112998762E-5</v>
       </c>
       <c r="J15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8933502605914002E-5</v>
       </c>
       <c r="K15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8879951421691985E-5</v>
       </c>
       <c r="L15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8825613609905036E-5</v>
       </c>
       <c r="M15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8768189797671407E-5</v>
       </c>
       <c r="N15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8706469788737519E-5</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8641058681230087E-5</v>
       </c>
       <c r="P15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8567841807886946E-5</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8487545286460116E-5</v>
       </c>
       <c r="R15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.1919812492497818E-5</v>
       </c>
       <c r="S15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.1830530263888033E-5</v>
       </c>
       <c r="T15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.173108238674788E-5</v>
       </c>
       <c r="U15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.1618201331192773E-5</v>
       </c>
       <c r="V15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.4991380705148162E-5</v>
       </c>
       <c r="W15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.4867033040090055E-5</v>
       </c>
       <c r="X15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.4726741039390805E-5</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.4567237173165427E-5</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.4385072382091385E-5</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.4175738685123882E-5</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.3947193122630346E-5</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.0142731045712066E-5</v>
       </c>
+      <c r="AL15">
+        <f t="shared" ref="AL15:BE15" si="7">AL4/btu_per_EJ</f>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AM15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AN15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AO15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AQ15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AR15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AS15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AT15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AU15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AV15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AW15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AX15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AY15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="AZ15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="BA15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="BB15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="BC15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="BD15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
+      <c r="BE15">
+        <f t="shared" si="7"/>
+        <v>5.0142731045712066E-5</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>2</v>
       </c>
       <c r="B16" t="e">
-        <f t="shared" ref="B16:AK16" si="2">B5/btu_per_EJ</f>
+        <f t="shared" ref="B16:AK16" si="8">B5/btu_per_EJ</f>
         <v>#VALUE!</v>
       </c>
       <c r="C16" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="D16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.1409440039699114E-5</v>
       </c>
       <c r="E16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.4389213948950193E-5</v>
       </c>
       <c r="F16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.3883030550930331E-5</v>
       </c>
       <c r="G16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.1749481848994347E-5</v>
       </c>
       <c r="H16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.5756427408434974E-5</v>
       </c>
       <c r="I16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.336492986801209E-5</v>
       </c>
       <c r="J16" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="K16" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="L16" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
       <c r="M16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.2574478419043644E-5</v>
       </c>
       <c r="N16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.2971640945765467E-5</v>
       </c>
       <c r="O16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.3468304652625816E-5</v>
       </c>
       <c r="P16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.3932462349838967E-5</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.4394859968691324E-5</v>
       </c>
       <c r="R16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.4863632610497585E-5</v>
       </c>
       <c r="S16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.5459626496358705E-5</v>
       </c>
       <c r="T16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.606450630512097E-5</v>
       </c>
       <c r="U16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.6646401847303939E-5</v>
       </c>
       <c r="V16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.7248294132678887E-5</v>
       </c>
       <c r="W16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.7855714311710578E-5</v>
       </c>
       <c r="X16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.8391126373664574E-5</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.9050959866771029E-5</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.980082686318496E-5</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.0469193469775478E-5</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.1157164251664075E-5</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.185914684886426E-5</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.2575426643184288E-5</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.3306294827051657E-5</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.4052048505275682E-5</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.4812990857866973E-5</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.55894312214466E-5</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.6381685262242366E-5</v>
       </c>
       <c r="AJ16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.7190075037145769E-5</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>3.8014929197236589E-5</v>
       </c>
+      <c r="AL16">
+        <f t="shared" ref="AL16:BE16" si="9">AL5/btu_per_EJ</f>
+        <v>3.878928287984439E-5</v>
+      </c>
+      <c r="AM16">
+        <f t="shared" si="9"/>
+        <v>3.9596648348006398E-5</v>
+      </c>
+      <c r="AN16">
+        <f t="shared" si="9"/>
+        <v>4.0404013816168412E-5</v>
+      </c>
+      <c r="AO16">
+        <f t="shared" si="9"/>
+        <v>4.1211379284330426E-5</v>
+      </c>
+      <c r="AP16">
+        <f t="shared" si="9"/>
+        <v>4.2018744752492434E-5</v>
+      </c>
+      <c r="AQ16">
+        <f t="shared" si="9"/>
+        <v>4.2826110220654448E-5</v>
+      </c>
+      <c r="AR16">
+        <f t="shared" si="9"/>
+        <v>4.3633475688816462E-5</v>
+      </c>
+      <c r="AS16">
+        <f t="shared" si="9"/>
+        <v>4.444084115697847E-5</v>
+      </c>
+      <c r="AT16">
+        <f t="shared" si="9"/>
+        <v>4.5248206625140484E-5</v>
+      </c>
+      <c r="AU16">
+        <f t="shared" si="9"/>
+        <v>4.6055572093302499E-5</v>
+      </c>
+      <c r="AV16">
+        <f t="shared" si="9"/>
+        <v>4.6862937561464506E-5</v>
+      </c>
+      <c r="AW16">
+        <f t="shared" si="9"/>
+        <v>4.767030302962652E-5</v>
+      </c>
+      <c r="AX16">
+        <f t="shared" si="9"/>
+        <v>4.8477668497788535E-5</v>
+      </c>
+      <c r="AY16">
+        <f t="shared" si="9"/>
+        <v>4.9285033965950542E-5</v>
+      </c>
+      <c r="AZ16">
+        <f t="shared" si="9"/>
+        <v>5.0092399434112557E-5</v>
+      </c>
+      <c r="BA16">
+        <f t="shared" si="9"/>
+        <v>5.0899764902274571E-5</v>
+      </c>
+      <c r="BB16">
+        <f t="shared" si="9"/>
+        <v>5.1707130370436585E-5</v>
+      </c>
+      <c r="BC16">
+        <f t="shared" si="9"/>
+        <v>5.2514495838598599E-5</v>
+      </c>
+      <c r="BD16">
+        <f t="shared" si="9"/>
+        <v>5.3321861306760607E-5</v>
+      </c>
+      <c r="BE16">
+        <f t="shared" si="9"/>
+        <v>5.4129226774922621E-5</v>
+      </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>4</v>
       </c>
       <c r="B17" t="e">
-        <f t="shared" ref="B17:AK17" si="3">B6/btu_per_EJ</f>
+        <f t="shared" ref="B17:AK17" si="10">B6/btu_per_EJ</f>
         <v>#VALUE!</v>
       </c>
       <c r="C17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="D17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.4318294060856061E-5</v>
       </c>
       <c r="E17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.4929649377579403E-5</v>
       </c>
       <c r="F17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.4922753202735881E-5</v>
       </c>
       <c r="G17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.5329274053872647E-5</v>
       </c>
       <c r="H17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.5462843163267301E-5</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.7559371725682696E-5</v>
       </c>
       <c r="J17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.4017814501292296E-5</v>
       </c>
       <c r="K17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.5456794124053592E-5</v>
       </c>
       <c r="L17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.5541109135681677E-5</v>
       </c>
       <c r="M17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.4327459219902568E-5</v>
       </c>
       <c r="N17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.4395953930841428E-5</v>
       </c>
       <c r="O17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.4372636108862221E-5</v>
       </c>
       <c r="P17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>3.5869354692678167E-5</v>
       </c>
       <c r="Q17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="R17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="S17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="T17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="U17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="V17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="W17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="X17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="Y17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="Z17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AA17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AB17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AC17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AD17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AE17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AF17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AG17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AH17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AI17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AJ17" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>4.4243592873182117E-5</v>
       </c>
+      <c r="AL17">
+        <f t="shared" ref="AL17:BE17" si="11">AL6/btu_per_EJ</f>
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>5</v>
       </c>
       <c r="B18">
-        <f t="shared" ref="B18:AK18" si="4">B7/btu_per_EJ</f>
+        <f t="shared" ref="B18:AK18" si="12">B7/btu_per_EJ</f>
         <v>1.6202771517590864E-5</v>
       </c>
       <c r="C18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>1.8915267376315273E-5</v>
       </c>
       <c r="D18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>1.9925204798944127E-5</v>
       </c>
       <c r="E18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.0060193613214753E-5</v>
       </c>
       <c r="F18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.0208212888926191E-5</v>
       </c>
       <c r="G18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.0551826212060509E-5</v>
       </c>
       <c r="H18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.092966297276293E-5</v>
       </c>
       <c r="I18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.1232098432175502E-5</v>
       </c>
       <c r="J18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.1529302391352033E-5</v>
       </c>
       <c r="K18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.1819722505545479E-5</v>
       </c>
       <c r="L18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.2202830864019846E-5</v>
       </c>
       <c r="M18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.2574842331297094E-5</v>
       </c>
       <c r="N18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.2971795941127227E-5</v>
       </c>
       <c r="O18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.346845654044158E-5</v>
       </c>
       <c r="P18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.3932622398539605E-5</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.4394859968691324E-5</v>
       </c>
       <c r="R18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.4863632610497585E-5</v>
       </c>
       <c r="S18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.5459626496358705E-5</v>
       </c>
       <c r="T18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.606450630512097E-5</v>
       </c>
       <c r="U18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.6646401847303939E-5</v>
       </c>
       <c r="V18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.7248294132678887E-5</v>
       </c>
       <c r="W18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.7855714311710578E-5</v>
       </c>
       <c r="X18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.8391126373664574E-5</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.9050959866771029E-5</v>
       </c>
       <c r="Z18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>2.980082686318496E-5</v>
       </c>
       <c r="AA18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.0469193469775478E-5</v>
       </c>
       <c r="AB18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.1157164251664075E-5</v>
       </c>
       <c r="AC18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.185914684886426E-5</v>
       </c>
       <c r="AD18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.2575426643184288E-5</v>
       </c>
       <c r="AE18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.3306294827051657E-5</v>
       </c>
       <c r="AF18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.4052048505275682E-5</v>
       </c>
       <c r="AG18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.4812990857866973E-5</v>
       </c>
       <c r="AH18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.55894312214466E-5</v>
       </c>
       <c r="AI18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.6381685262242366E-5</v>
       </c>
       <c r="AJ18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.7190075037145769E-5</v>
       </c>
       <c r="AK18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>3.8015253525197351E-5</v>
       </c>
+      <c r="AL18">
+        <f t="shared" ref="AL18:BE18" si="13">AL7/btu_per_EJ</f>
+        <v>3.8824074179411196E-5</v>
+      </c>
+      <c r="AM18">
+        <f t="shared" si="13"/>
+        <v>3.9632960126398162E-5</v>
+      </c>
+      <c r="AN18">
+        <f t="shared" si="13"/>
+        <v>4.0441846073385127E-5</v>
+      </c>
+      <c r="AO18">
+        <f t="shared" si="13"/>
+        <v>4.1250732020372093E-5</v>
+      </c>
+      <c r="AP18">
+        <f t="shared" si="13"/>
+        <v>4.2059617967359059E-5</v>
+      </c>
+      <c r="AQ18">
+        <f t="shared" si="13"/>
+        <v>4.2868503914346025E-5</v>
+      </c>
+      <c r="AR18">
+        <f t="shared" si="13"/>
+        <v>4.3677389861332991E-5</v>
+      </c>
+      <c r="AS18">
+        <f t="shared" si="13"/>
+        <v>4.4486275808319956E-5</v>
+      </c>
+      <c r="AT18">
+        <f t="shared" si="13"/>
+        <v>4.5295161755306922E-5</v>
+      </c>
+      <c r="AU18">
+        <f t="shared" si="13"/>
+        <v>4.6104047702293888E-5</v>
+      </c>
+      <c r="AV18">
+        <f t="shared" si="13"/>
+        <v>4.6912933649280854E-5</v>
+      </c>
+      <c r="AW18">
+        <f t="shared" si="13"/>
+        <v>4.772181959626782E-5</v>
+      </c>
+      <c r="AX18">
+        <f t="shared" si="13"/>
+        <v>4.8530705543254792E-5</v>
+      </c>
+      <c r="AY18">
+        <f t="shared" si="13"/>
+        <v>4.9339591490241751E-5</v>
+      </c>
+      <c r="AZ18">
+        <f t="shared" si="13"/>
+        <v>5.0148477437228724E-5</v>
+      </c>
+      <c r="BA18">
+        <f t="shared" si="13"/>
+        <v>5.0957363384215683E-5</v>
+      </c>
+      <c r="BB18">
+        <f t="shared" si="13"/>
+        <v>5.1766249331202655E-5</v>
+      </c>
+      <c r="BC18">
+        <f t="shared" si="13"/>
+        <v>5.2575135278189615E-5</v>
+      </c>
+      <c r="BD18">
+        <f t="shared" si="13"/>
+        <v>5.3384021225176587E-5</v>
+      </c>
+      <c r="BE18">
+        <f t="shared" si="13"/>
+        <v>5.4192907172163546E-5</v>
+      </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>6</v>
       </c>
       <c r="B19">
-        <f t="shared" ref="B19:AK19" si="5">B8/btu_per_EJ</f>
+        <f t="shared" ref="B19:AK19" si="14">B8/btu_per_EJ</f>
         <v>1.7551132278158152E-5</v>
       </c>
       <c r="C19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.0176808701133611E-5</v>
       </c>
       <c r="D19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.3231602523694866E-5</v>
       </c>
       <c r="E19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.3761198167222491E-5</v>
       </c>
       <c r="F19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.4561673017219928E-5</v>
       </c>
       <c r="G19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.5515011770568887E-5</v>
       </c>
       <c r="H19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.6497153930290583E-5</v>
       </c>
       <c r="I19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.772006414520778E-5</v>
       </c>
       <c r="J19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.8605925463379367E-5</v>
       </c>
       <c r="K19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.8671178338332292E-5</v>
       </c>
       <c r="L19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.8765134749910194E-5</v>
       </c>
       <c r="M19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.8866332994762323E-5</v>
       </c>
       <c r="N19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.8970723326439491E-5</v>
       </c>
       <c r="O19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.925194865172028E-5</v>
       </c>
       <c r="P19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.9400749073399202E-5</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>2.9533244208656942E-5</v>
       </c>
       <c r="R19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.1208634778709106E-5</v>
       </c>
       <c r="S19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.1385733364497993E-5</v>
       </c>
       <c r="T19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.159561793570684E-5</v>
       </c>
       <c r="U19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.1880250653125256E-5</v>
       </c>
       <c r="V19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.3400680931207279E-5</v>
       </c>
       <c r="W19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.3649418594603569E-5</v>
       </c>
       <c r="X19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.3869646827804504E-5</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.4207025538319675E-5</v>
       </c>
       <c r="Z19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.4575624977024262E-5</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.4910104904348212E-5</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.5335962937616282E-5</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.6739082314998908E-5</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.7381038557961687E-5</v>
       </c>
       <c r="AE19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.7879860304153716E-5</v>
       </c>
       <c r="AF19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.8378040327458953E-5</v>
       </c>
       <c r="AG19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.8917125312318058E-5</v>
       </c>
       <c r="AH19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>3.9496551786362013E-5</v>
       </c>
       <c r="AI19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>4.0115976753177347E-5</v>
       </c>
       <c r="AJ19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>4.0775109725166814E-5</v>
       </c>
       <c r="AK19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>4.1473808251362669E-5</v>
       </c>
+      <c r="AL19">
+        <f t="shared" ref="AL19:BE19" si="15">AL8/btu_per_EJ</f>
+        <v>4.2010796753617773E-5</v>
+      </c>
+      <c r="AM19">
+        <f t="shared" si="15"/>
+        <v>4.2563533408887683E-5</v>
+      </c>
+      <c r="AN19">
+        <f t="shared" si="15"/>
+        <v>4.3116270064157586E-5</v>
+      </c>
+      <c r="AO19">
+        <f t="shared" si="15"/>
+        <v>4.3669006719427496E-5</v>
+      </c>
+      <c r="AP19">
+        <f t="shared" si="15"/>
+        <v>4.4221743374697413E-5</v>
+      </c>
+      <c r="AQ19">
+        <f t="shared" si="15"/>
+        <v>4.4774480029967316E-5</v>
+      </c>
+      <c r="AR19">
+        <f t="shared" si="15"/>
+        <v>4.5327216685237226E-5</v>
+      </c>
+      <c r="AS19">
+        <f t="shared" si="15"/>
+        <v>4.5879953340507136E-5</v>
+      </c>
+      <c r="AT19">
+        <f t="shared" si="15"/>
+        <v>4.6432689995777039E-5</v>
+      </c>
+      <c r="AU19">
+        <f t="shared" si="15"/>
+        <v>4.6985426651046949E-5</v>
+      </c>
+      <c r="AV19">
+        <f t="shared" si="15"/>
+        <v>4.7538163306316859E-5</v>
+      </c>
+      <c r="AW19">
+        <f t="shared" si="15"/>
+        <v>4.8090899961586762E-5</v>
+      </c>
+      <c r="AX19">
+        <f t="shared" si="15"/>
+        <v>4.8643636616856672E-5</v>
+      </c>
+      <c r="AY19">
+        <f t="shared" si="15"/>
+        <v>4.9196373272126575E-5</v>
+      </c>
+      <c r="AZ19">
+        <f t="shared" si="15"/>
+        <v>4.9749109927396485E-5</v>
+      </c>
+      <c r="BA19">
+        <f t="shared" si="15"/>
+        <v>5.0301846582666401E-5</v>
+      </c>
+      <c r="BB19">
+        <f t="shared" si="15"/>
+        <v>5.0854583237936298E-5</v>
+      </c>
+      <c r="BC19">
+        <f t="shared" si="15"/>
+        <v>5.1407319893206214E-5</v>
+      </c>
+      <c r="BD19">
+        <f t="shared" si="15"/>
+        <v>5.1960056548476124E-5</v>
+      </c>
+      <c r="BE19">
+        <f t="shared" si="15"/>
+        <v>5.2512793203746027E-5</v>
+      </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>7</v>
       </c>
       <c r="B20">
-        <f t="shared" ref="B20:AK20" si="6">B9/btu_per_EJ</f>
+        <f t="shared" ref="B20:AK20" si="16">B9/btu_per_EJ</f>
         <v>0</v>
       </c>
       <c r="C20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="D20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="P20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="R20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="S20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="T20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="U20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="V20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="W20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="X20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AD20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AG20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AH20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AI20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AJ20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AK20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <f t="shared" ref="AL20:BE20" si="17">AL9/btu_per_EJ</f>
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>0</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:AK21" si="7">B10/btu_per_EJ</f>
+        <f t="shared" ref="B21:AK21" si="18">B10/btu_per_EJ</f>
         <v>3.2534468284018547E-5</v>
       </c>
       <c r="C21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.5737832403189339E-5</v>
       </c>
       <c r="D21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8702911199423575E-5</v>
       </c>
       <c r="E21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8933789668806468E-5</v>
       </c>
       <c r="F21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8818500756131412E-5</v>
       </c>
       <c r="G21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8996058362820982E-5</v>
       </c>
       <c r="H21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.9180888790480071E-5</v>
       </c>
       <c r="I21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.9252777251332621E-5</v>
       </c>
       <c r="J21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.876796989760894E-5</v>
       </c>
       <c r="K21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8955066361771352E-5</v>
       </c>
       <c r="L21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.892563410474206E-5</v>
       </c>
       <c r="M21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8894155433113717E-5</v>
       </c>
       <c r="N21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8858072328637091E-5</v>
       </c>
       <c r="O21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8800732816407668E-5</v>
       </c>
       <c r="P21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8930946033858302E-5</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8788921528331964E-5</v>
       </c>
       <c r="R21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.1713392353940595E-5</v>
       </c>
       <c r="S21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.1622568678008901E-5</v>
       </c>
       <c r="T21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.1398350978222789E-5</v>
       </c>
       <c r="U21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.1106147585989588E-5</v>
       </c>
       <c r="V21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.3333611971477894E-5</v>
       </c>
       <c r="W21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.2828859173333252E-5</v>
       </c>
       <c r="X21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.1901977294732659E-5</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.0670534412304667E-5</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.0995338871255461E-5</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.9684472820734024E-5</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.9037430761406795E-5</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.2219842960559737E-5</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.0832119985502794E-5</v>
       </c>
       <c r="AE21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.7694999143942138E-5</v>
       </c>
       <c r="AF21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.6904915774644164E-5</v>
       </c>
       <c r="AG21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.7699828952329217E-5</v>
       </c>
       <c r="AH21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.8510584666979635E-5</v>
       </c>
       <c r="AI21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>3.9337498666232791E-5</v>
       </c>
       <c r="AJ21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.0180892986627953E-5</v>
       </c>
       <c r="AK21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>4.1041096075720387E-5</v>
       </c>
+      <c r="AL21">
+        <f t="shared" ref="AL21:BE21" si="19">AL10/btu_per_EJ</f>
+        <v>4.1114423642562152E-5</v>
+      </c>
+      <c r="AM21">
+        <f t="shared" si="19"/>
+        <v>4.1187751209403924E-5</v>
+      </c>
+      <c r="AN21">
+        <f t="shared" si="19"/>
+        <v>4.1261078776245689E-5</v>
+      </c>
+      <c r="AO21">
+        <f t="shared" si="19"/>
+        <v>4.1334406343087461E-5</v>
+      </c>
+      <c r="AP21">
+        <f t="shared" si="19"/>
+        <v>4.1407733909929227E-5</v>
+      </c>
+      <c r="AQ21">
+        <f t="shared" si="19"/>
+        <v>4.1481061476770992E-5</v>
+      </c>
+      <c r="AR21">
+        <f t="shared" si="19"/>
+        <v>4.1554389043612764E-5</v>
+      </c>
+      <c r="AS21">
+        <f t="shared" si="19"/>
+        <v>4.1627716610454529E-5</v>
+      </c>
+      <c r="AT21">
+        <f t="shared" si="19"/>
+        <v>4.1701044177296301E-5</v>
+      </c>
+      <c r="AU21">
+        <f t="shared" si="19"/>
+        <v>4.177437174413806E-5</v>
+      </c>
+      <c r="AV21">
+        <f t="shared" si="19"/>
+        <v>4.1847699310979832E-5</v>
+      </c>
+      <c r="AW21">
+        <f t="shared" si="19"/>
+        <v>4.1921026877821597E-5</v>
+      </c>
+      <c r="AX21">
+        <f t="shared" si="19"/>
+        <v>4.1994354444663362E-5</v>
+      </c>
+      <c r="AY21">
+        <f t="shared" si="19"/>
+        <v>4.2067682011505135E-5</v>
+      </c>
+      <c r="AZ21">
+        <f t="shared" si="19"/>
+        <v>4.21410095783469E-5</v>
+      </c>
+      <c r="BA21">
+        <f t="shared" si="19"/>
+        <v>4.2214337145188672E-5</v>
+      </c>
+      <c r="BB21">
+        <f t="shared" si="19"/>
+        <v>4.2287664712030437E-5</v>
+      </c>
+      <c r="BC21">
+        <f t="shared" si="19"/>
+        <v>4.2360992278872202E-5</v>
+      </c>
+      <c r="BD21">
+        <f t="shared" si="19"/>
+        <v>4.2434319845713975E-5</v>
+      </c>
+      <c r="BE21">
+        <f t="shared" si="19"/>
+        <v>4.250764741255574E-5</v>
+      </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>1</v>
       </c>
       <c r="B22">
-        <f t="shared" ref="B22:AK22" si="8">B11/btu_per_EJ</f>
+        <f t="shared" ref="B22:AK22" si="20">B11/btu_per_EJ</f>
         <v>3.2684379576442442E-5</v>
       </c>
       <c r="C22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.5904835850454043E-5</v>
       </c>
       <c r="D22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.8910690406533591E-5</v>
       </c>
       <c r="E22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9117845750244623E-5</v>
       </c>
       <c r="F22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.930938956228413E-5</v>
       </c>
       <c r="G22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9482266097111853E-5</v>
       </c>
       <c r="H22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9614903606507026E-5</v>
       </c>
       <c r="I22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9730931172321509E-5</v>
       </c>
       <c r="J22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.8951141216310381E-5</v>
       </c>
       <c r="K22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.913923596902712E-5</v>
       </c>
       <c r="L22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9109646670626398E-5</v>
       </c>
       <c r="M22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9078000038594684E-5</v>
       </c>
       <c r="N22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9041724405892776E-5</v>
       </c>
       <c r="O22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9000971047052621E-5</v>
       </c>
       <c r="P22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.9140052851498292E-5</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>3.909445870764373E-5</v>
       </c>
       <c r="R22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.2262025738111271E-5</v>
       </c>
       <c r="S22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.2203633768874846E-5</v>
       </c>
       <c r="T22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.2138767249681562E-5</v>
       </c>
       <c r="U22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.2066215984277853E-5</v>
       </c>
       <c r="V22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.5203286069154565E-5</v>
       </c>
       <c r="W22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.5110282487064909E-5</v>
       </c>
       <c r="X22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.5004753373750413E-5</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.4884762415205377E-5</v>
       </c>
       <c r="Z22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.4985450743505458E-5</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.4846278174340744E-5</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>4.469388421110541E-5</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0952715398250774E-5</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0742927877688159E-5</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.049299209641212E-5</v>
       </c>
       <c r="AF22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0189353856382228E-5</v>
       </c>
       <c r="AG22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AH22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AI22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AJ22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0142731045712066E-5</v>
       </c>
       <c r="AK22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="20"/>
         <v>5.0142731045712066E-5</v>
       </c>
+      <c r="AL22">
+        <f t="shared" ref="AL22:BE22" si="21">AL11/btu_per_EJ</f>
+        <v>5.1041904137028587E-5</v>
+      </c>
+      <c r="AM22">
+        <f t="shared" si="21"/>
+        <v>5.1492180427746929E-5</v>
+      </c>
+      <c r="AN22">
+        <f t="shared" si="21"/>
+        <v>5.1942456718465285E-5</v>
+      </c>
+      <c r="AO22">
+        <f t="shared" si="21"/>
+        <v>5.2392733009183627E-5</v>
+      </c>
+      <c r="AP22">
+        <f t="shared" si="21"/>
+        <v>5.2843009299901969E-5</v>
+      </c>
+      <c r="AQ22">
+        <f t="shared" si="21"/>
+        <v>5.3293285590620312E-5</v>
+      </c>
+      <c r="AR22">
+        <f t="shared" si="21"/>
+        <v>5.3743561881338654E-5</v>
+      </c>
+      <c r="AS22">
+        <f t="shared" si="21"/>
+        <v>5.4193838172057003E-5</v>
+      </c>
+      <c r="AT22">
+        <f t="shared" si="21"/>
+        <v>5.4644114462775345E-5</v>
+      </c>
+      <c r="AU22">
+        <f t="shared" si="21"/>
+        <v>5.5094390753493688E-5</v>
+      </c>
+      <c r="AV22">
+        <f t="shared" si="21"/>
+        <v>5.554466704421203E-5</v>
+      </c>
+      <c r="AW22">
+        <f t="shared" si="21"/>
+        <v>5.5994943334930379E-5</v>
+      </c>
+      <c r="AX22">
+        <f t="shared" si="21"/>
+        <v>5.6445219625648721E-5</v>
+      </c>
+      <c r="AY22">
+        <f t="shared" si="21"/>
+        <v>5.6895495916367064E-5</v>
+      </c>
+      <c r="AZ22">
+        <f t="shared" si="21"/>
+        <v>5.7345772207085406E-5</v>
+      </c>
+      <c r="BA22">
+        <f t="shared" si="21"/>
+        <v>5.7796048497803748E-5</v>
+      </c>
+      <c r="BB22">
+        <f t="shared" si="21"/>
+        <v>5.8246324788522097E-5</v>
+      </c>
+      <c r="BC22">
+        <f t="shared" si="21"/>
+        <v>5.869660107924044E-5</v>
+      </c>
+      <c r="BD22">
+        <f t="shared" si="21"/>
+        <v>5.9146877369958782E-5</v>
+      </c>
+      <c r="BE22">
+        <f t="shared" si="21"/>
+        <v>5.9597153660677124E-5</v>
+      </c>
     </row>
-    <row r="24" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3085,7 +4448,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -3093,7 +4456,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -3101,7 +4464,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -3109,12 +4472,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:57" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:57" x14ac:dyDescent="0.45">
       <c r="B31">
         <v>2015</v>
       </c>
@@ -3223,8 +4586,68 @@
       <c r="AK31">
         <v>2050</v>
       </c>
+      <c r="AL31">
+        <v>2051</v>
+      </c>
+      <c r="AM31">
+        <v>2052</v>
+      </c>
+      <c r="AN31">
+        <v>2053</v>
+      </c>
+      <c r="AO31">
+        <v>2054</v>
+      </c>
+      <c r="AP31">
+        <v>2055</v>
+      </c>
+      <c r="AQ31">
+        <v>2056</v>
+      </c>
+      <c r="AR31">
+        <v>2057</v>
+      </c>
+      <c r="AS31">
+        <v>2058</v>
+      </c>
+      <c r="AT31">
+        <v>2059</v>
+      </c>
+      <c r="AU31">
+        <v>2060</v>
+      </c>
+      <c r="AV31">
+        <v>2061</v>
+      </c>
+      <c r="AW31">
+        <v>2062</v>
+      </c>
+      <c r="AX31">
+        <v>2063</v>
+      </c>
+      <c r="AY31">
+        <v>2064</v>
+      </c>
+      <c r="AZ31">
+        <v>2065</v>
+      </c>
+      <c r="BA31">
+        <v>2066</v>
+      </c>
+      <c r="BB31">
+        <v>2067</v>
+      </c>
+      <c r="BC31">
+        <v>2068</v>
+      </c>
+      <c r="BD31">
+        <v>2069</v>
+      </c>
+      <c r="BE31">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3336,8 +4759,68 @@
       <c r="AK32">
         <v>0</v>
       </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32">
+        <v>0</v>
+      </c>
+      <c r="AV32">
+        <v>0</v>
+      </c>
+      <c r="AW32">
+        <v>0</v>
+      </c>
+      <c r="AX32">
+        <v>0</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -3449,8 +4932,68 @@
       <c r="AK33">
         <v>0</v>
       </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="AV33">
+        <v>0</v>
+      </c>
+      <c r="AW33">
+        <v>0</v>
+      </c>
+      <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>0</v>
+      </c>
+      <c r="BB33">
+        <v>0</v>
+      </c>
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -3598,8 +5141,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -3608,144 +5231,224 @@
         <v>1.4983336005860395E-5</v>
       </c>
       <c r="C35">
-        <f t="shared" ref="C35:AK35" si="9">C21-C19</f>
+        <f t="shared" ref="C35:AK35" si="22">C21-C19</f>
         <v>1.5561023702055728E-5</v>
       </c>
       <c r="D35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.547130867572871E-5</v>
       </c>
       <c r="E35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.5172591501583976E-5</v>
       </c>
       <c r="F35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.4256827738911485E-5</v>
       </c>
       <c r="G35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.3481046592252095E-5</v>
       </c>
       <c r="H35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.2683734860189488E-5</v>
       </c>
       <c r="I35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.153271310612484E-5</v>
       </c>
       <c r="J35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.0162044434229573E-5</v>
       </c>
       <c r="K35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.0283888023439061E-5</v>
       </c>
       <c r="L35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.0160499354831865E-5</v>
       </c>
       <c r="M35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.0027822438351394E-5</v>
       </c>
       <c r="N35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.8873490021975999E-6</v>
       </c>
       <c r="O35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.5487841646873881E-6</v>
       </c>
       <c r="P35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.5301969604591001E-6</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.2556773196750223E-6</v>
       </c>
       <c r="R35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.050475757523149E-5</v>
       </c>
       <c r="S35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>1.0236835313510908E-5</v>
       </c>
       <c r="T35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.8027330425159485E-6</v>
       </c>
       <c r="U35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.2258969328643323E-6</v>
       </c>
       <c r="V35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.9329310402706153E-6</v>
       </c>
       <c r="W35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>9.1794405787296826E-6</v>
       </c>
       <c r="X35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>8.0323304669281553E-6</v>
       </c>
       <c r="Y35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>6.4635088739849921E-6</v>
       </c>
       <c r="Z35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>6.4197138942311997E-6</v>
       </c>
       <c r="AA35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>4.7743679163858121E-6</v>
       </c>
       <c r="AB35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>3.7014678237905137E-6</v>
       </c>
       <c r="AC35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>5.4807606455608285E-6</v>
       </c>
       <c r="AD35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>3.4510814275411062E-6</v>
       </c>
       <c r="AE35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-1.8486116021157808E-7</v>
       </c>
       <c r="AF35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-1.4731245528147894E-6</v>
       </c>
       <c r="AG35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-1.2172963599888417E-6</v>
       </c>
       <c r="AH35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-9.8596711938237885E-7</v>
       </c>
       <c r="AI35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-7.7847808694455668E-7</v>
       </c>
       <c r="AJ35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-5.9421673853886088E-7</v>
       </c>
       <c r="AK35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="22"/>
         <v>-4.3271217564228297E-7</v>
+      </c>
+      <c r="AL35">
+        <f t="shared" ref="AL35:BE35" si="23">AL21-AL19</f>
+        <v>-8.9637311105562125E-7</v>
+      </c>
+      <c r="AM35">
+        <f t="shared" si="23"/>
+        <v>-1.3757821994837591E-6</v>
+      </c>
+      <c r="AN35">
+        <f t="shared" si="23"/>
+        <v>-1.8551912879118969E-6</v>
+      </c>
+      <c r="AO35">
+        <f t="shared" si="23"/>
+        <v>-2.3346003763400348E-6</v>
+      </c>
+      <c r="AP35">
+        <f t="shared" si="23"/>
+        <v>-2.8140094647681861E-6</v>
+      </c>
+      <c r="AQ35">
+        <f t="shared" si="23"/>
+        <v>-3.293418553196324E-6</v>
+      </c>
+      <c r="AR35">
+        <f t="shared" si="23"/>
+        <v>-3.7728276416244618E-6</v>
+      </c>
+      <c r="AS35">
+        <f t="shared" si="23"/>
+        <v>-4.2522367300526064E-6</v>
+      </c>
+      <c r="AT35">
+        <f t="shared" si="23"/>
+        <v>-4.7316458184807375E-6</v>
+      </c>
+      <c r="AU35">
+        <f t="shared" si="23"/>
+        <v>-5.2110549069088889E-6</v>
+      </c>
+      <c r="AV35">
+        <f t="shared" si="23"/>
+        <v>-5.6904639953370267E-6</v>
+      </c>
+      <c r="AW35">
+        <f t="shared" si="23"/>
+        <v>-6.1698730837651645E-6</v>
+      </c>
+      <c r="AX35">
+        <f t="shared" si="23"/>
+        <v>-6.6492821721933092E-6</v>
+      </c>
+      <c r="AY35">
+        <f t="shared" si="23"/>
+        <v>-7.1286912606214402E-6</v>
+      </c>
+      <c r="AZ35">
+        <f t="shared" si="23"/>
+        <v>-7.6081003490495848E-6</v>
+      </c>
+      <c r="BA35">
+        <f t="shared" si="23"/>
+        <v>-8.0875094374777294E-6</v>
+      </c>
+      <c r="BB35">
+        <f t="shared" si="23"/>
+        <v>-8.5669185259058605E-6</v>
+      </c>
+      <c r="BC35">
+        <f t="shared" si="23"/>
+        <v>-9.0463276143340119E-6</v>
+      </c>
+      <c r="BD35">
+        <f t="shared" si="23"/>
+        <v>-9.5257367027621497E-6</v>
+      </c>
+      <c r="BE35">
+        <f t="shared" si="23"/>
+        <v>-1.0005145791190288E-5</v>
       </c>
     </row>
   </sheetData>
@@ -3754,18 +5457,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BE11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="23.86328125" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -3877,8 +5580,68 @@
       <c r="AK1">
         <v>2050</v>
       </c>
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4026,8 +5789,88 @@
         <f>Calcs!AK32</f>
         <v>0</v>
       </c>
+      <c r="AL2">
+        <f>Calcs!AL32</f>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f>Calcs!AM32</f>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f>Calcs!AN32</f>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f>Calcs!AO32</f>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f>Calcs!AP32</f>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f>Calcs!AQ32</f>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f>Calcs!AR32</f>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f>Calcs!AS32</f>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f>Calcs!AT32</f>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f>Calcs!AU32</f>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f>Calcs!AV32</f>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f>Calcs!AW32</f>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f>Calcs!AX32</f>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f>Calcs!AY32</f>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f>Calcs!AZ32</f>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f>Calcs!BA32</f>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f>Calcs!BB32</f>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f>Calcs!BC32</f>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f>Calcs!BD32</f>
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <f>Calcs!BE32</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4175,8 +6018,88 @@
         <f>Calcs!AK33</f>
         <v>0</v>
       </c>
+      <c r="AL3">
+        <f>Calcs!AL33</f>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f>Calcs!AM33</f>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f>Calcs!AN33</f>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f>Calcs!AO33</f>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f>Calcs!AP33</f>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f>Calcs!AQ33</f>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f>Calcs!AR33</f>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f>Calcs!AS33</f>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f>Calcs!AT33</f>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f>Calcs!AU33</f>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f>Calcs!AV33</f>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f>Calcs!AW33</f>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f>Calcs!AX33</f>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f>Calcs!AY33</f>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f>Calcs!AZ33</f>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f>Calcs!BA33</f>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f>Calcs!BB33</f>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f>Calcs!BC33</f>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f>Calcs!BD33</f>
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <f>Calcs!BE33</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -4324,8 +6247,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4473,8 +6476,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4622,8 +6705,88 @@
         <f>Calcs!AK34</f>
         <v>0</v>
       </c>
+      <c r="AL6">
+        <f>Calcs!AL34</f>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f>Calcs!AM34</f>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f>Calcs!AN34</f>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f>Calcs!AO34</f>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f>Calcs!AP34</f>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f>Calcs!AQ34</f>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f>Calcs!AR34</f>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f>Calcs!AS34</f>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f>Calcs!AT34</f>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f>Calcs!AU34</f>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f>Calcs!AV34</f>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f>Calcs!AW34</f>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f>Calcs!AX34</f>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f>Calcs!AY34</f>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f>Calcs!AZ34</f>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f>Calcs!BA34</f>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f>Calcs!BB34</f>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f>Calcs!BC34</f>
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <f>Calcs!BD34</f>
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <f>Calcs!BE34</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4771,8 +6934,88 @@
         <f>MAX(Calcs!AK35,0)</f>
         <v>0</v>
       </c>
+      <c r="AL7">
+        <f>MAX(Calcs!AL35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f>MAX(Calcs!AM35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f>MAX(Calcs!AN35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f>MAX(Calcs!AO35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f>MAX(Calcs!AP35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f>MAX(Calcs!AQ35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f>MAX(Calcs!AR35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f>MAX(Calcs!AS35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f>MAX(Calcs!AT35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f>MAX(Calcs!AU35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f>MAX(Calcs!AV35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f>MAX(Calcs!AW35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f>MAX(Calcs!AX35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f>MAX(Calcs!AY35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f>MAX(Calcs!AZ35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f>MAX(Calcs!BA35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f>MAX(Calcs!BB35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f>MAX(Calcs!BC35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f>MAX(Calcs!BD35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <f>MAX(Calcs!BE35,0)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -4920,8 +7163,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -5069,8 +7392,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5218,8 +7621,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <f>0</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -5364,6 +7847,86 @@
         <v>0</v>
       </c>
       <c r="AK11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="BE11">
         <f>0</f>
         <v>0</v>
       </c>
